--- a/sum.var_AMR_ES_C3G_R.xlsx
+++ b/sum.var_AMR_ES_C3G_R.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -50,9 +50,6 @@
     <t xml:space="preserve">log_AMC_ville_FQ</t>
   </si>
   <si>
-    <t xml:space="preserve">log_AMC_ville_aminoglycosides</t>
-  </si>
-  <si>
     <t xml:space="preserve">log_AMC_ville_macrolides</t>
   </si>
   <si>
@@ -74,6 +71,69 @@
     <t xml:space="preserve">log_AMC_ville_tot_except_FQ</t>
   </si>
   <si>
+    <t xml:space="preserve">AMR_animaux_production_C3G_R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMR_animaux_production_FQ_R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMR_ES_C3G_R.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">veto_by_AC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">veto_by_CV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prop_veto_50plus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tx_possession_chats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tx_possession_chevaux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_UGB_density_bovine_all</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_UGB_density_bovins_adultes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_UGB_density_lapins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_UGB_density_livestock_tot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_UGB_density_veaux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_UGB_density_volailles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMR_ES_C3G_R.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">air_NO2_pop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">air_O3_pop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">air_PM10_pop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">air_PM25_pop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dju_refroi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMR_ES_C3G_R.3</t>
+  </si>
+  <si>
     <t xml:space="preserve">bac_ou_plus_20_64</t>
   </si>
   <si>
@@ -89,15 +149,6 @@
     <t xml:space="preserve">unemployement_pourc</t>
   </si>
   <si>
-    <t xml:space="preserve">veto_by_AC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">veto_by_CV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prop_veto_50plus</t>
-  </si>
-  <si>
     <t xml:space="preserve">APL_medG</t>
   </si>
   <si>
@@ -108,45 +159,6 @@
   </si>
   <si>
     <t xml:space="preserve">couv_creche</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tx_possession_chats</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tx_possession_chevaux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">air_NO2_pop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">air_O3_pop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">air_PM10_pop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">air_PM25_pop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dju_refroi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_UGB_density_bovine_all</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_UGB_density_bovins_adultes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_UGB_density_lapins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_UGB_density_livestock_tot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_UGB_density_veaux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_UGB_density_volailles</t>
   </si>
   <si>
     <t xml:space="preserve">Auvergne-Rhone-Alpes</t>
@@ -647,1649 +659,1805 @@
       <c r="AS1" t="s">
         <v>44</v>
       </c>
+      <c r="AT1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.00556793499629644</v>
+        <v>-0.00192505045855437</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00333820264743013</v>
+        <v>-0.0324612627923965</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0533935096010106</v>
+        <v>0.00638968920047108</v>
       </c>
       <c r="E2" t="n">
-        <v>0.229225182819115</v>
+        <v>0.0525540277860457</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0312052760873627</v>
+        <v>-0.102039818199194</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00751919012345917</v>
+        <v>-0.0537738005079313</v>
       </c>
       <c r="H2" t="n">
-        <v>0.106143002981886</v>
+        <v>0.100795009558128</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0292745290823375</v>
+        <v>0.0374203753090823</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0999188767003226</v>
+        <v>0.045233547557697</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.103030049765665</v>
+        <v>-0.137537366935709</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.0396772269942912</v>
+        <v>-0.0506549855573347</v>
       </c>
       <c r="M2" t="n">
-        <v>0.000763123493420801</v>
+        <v>-0.119497492178242</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.12420711082142</v>
+        <v>-0.0901039848670477</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.0833362047662344</v>
+        <v>-0.0728650935910791</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.0607666805133019</v>
+        <v>-0.113630297435165</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.105320511062282</v>
+        <v>-0.0598704263170972</v>
       </c>
       <c r="R2" t="n">
-        <v>0.00191022555251561</v>
+        <v>0.0372468599562332</v>
       </c>
       <c r="S2" t="n">
-        <v>0.099552930335534</v>
+        <v>-0.115022957316709</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.10632951505456</v>
+        <v>-0.0061525067524421</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0195084240741962</v>
+        <v>-0.0110027515557436</v>
       </c>
       <c r="V2" t="n">
-        <v>0.06391291535433</v>
+        <v>-0.00192505045855437</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0163082867212111</v>
+        <v>0.153022366111796</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.0118103748837108</v>
+        <v>0.0572789883436409</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.00152496229816464</v>
+        <v>-0.013401295858147</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.250349523685717</v>
+        <v>-12.3491190226778</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.155228469004598</v>
+        <v>-4.38432001660486</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.012109123567263</v>
+        <v>0.375407250726009</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.18342381850517</v>
+        <v>0.357342469242618</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.131524475760531</v>
+        <v>-0.0109321781074568</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.101672060433269</v>
+        <v>0.152438110734191</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.014239766187334</v>
+        <v>0.235273003586518</v>
       </c>
       <c r="AG2" t="n">
-        <v>-13.7778198847377</v>
+        <v>-0.210225694021555</v>
       </c>
       <c r="AH2" t="n">
-        <v>-4.50268820676017</v>
+        <v>-0.00192505045855437</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.67366620645002</v>
+        <v>2.44759601801482</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-5.20655478700674</v>
+        <v>-2.0801748915393</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0.575217029341332</v>
+        <v>-0.147766882953508</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.0707017040871757</v>
+        <v>0.470798627558077</v>
       </c>
       <c r="AM2" t="n">
-        <v>-5.68581071199684</v>
+        <v>11.3963686512327</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.38297549099864</v>
+        <v>-0.00192505045855437</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.361041419807334</v>
+        <v>0.0230907538840277</v>
       </c>
       <c r="AP2" t="n">
-        <v>-0.00830283523775202</v>
+        <v>0.0712086262938508</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.151539696998256</v>
+        <v>0.016391769099467</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.255862647925165</v>
+        <v>-0.0134933444181438</v>
       </c>
       <c r="AS2" t="n">
-        <v>-0.212091836449402</v>
+        <v>-0.0118071359168294</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>-0.236834810022079</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0.102545270492877</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0.100965123810685</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0.0104281676230812</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.0140491305434764</v>
+        <v>-0.0187544909375068</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.0422526617423277</v>
+        <v>-0.0265758957390948</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0178770974190209</v>
+        <v>-0.0596585771517043</v>
       </c>
       <c r="E3" t="n">
-        <v>0.137054705706966</v>
+        <v>0.0828394450648569</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0537404240025266</v>
+        <v>0.0414821204140873</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.00145822657616187</v>
+        <v>0.0110392913343446</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0523321972721438</v>
+        <v>0.0358882860738656</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.280071548352838</v>
+        <v>-0.0977320093276271</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0512503296527898</v>
+        <v>0.0910089370534375</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0396710979059076</v>
+        <v>0.0678548142823489</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0140798894950997</v>
+        <v>-0.0112877020144233</v>
       </c>
       <c r="M3" t="n">
-        <v>0.00309885245921417</v>
+        <v>0.0307720366933086</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0180587842909492</v>
+        <v>-0.0160219843047286</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0121293684204653</v>
+        <v>0.013926091011938</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0143155269213644</v>
+        <v>0.0157652323762675</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.010803962173457</v>
+        <v>0.0185705856742391</v>
       </c>
       <c r="R3" t="n">
-        <v>0.000247954770138337</v>
+        <v>0.0985693679402339</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0500865502212396</v>
+        <v>0.0178150770664027</v>
       </c>
       <c r="T3" t="n">
-        <v>0.00975782858928002</v>
+        <v>-0.00650174649908075</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.00985195876913034</v>
+        <v>0.00654508778547107</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.136141432827287</v>
+        <v>-0.0187544909375068</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.01270445537361</v>
+        <v>-0.0265319628725331</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.010520906523809</v>
+        <v>-0.773703148659539</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.00289839877130694</v>
+        <v>0.0345761659603827</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.0660755628290678</v>
+        <v>3.15244881080114</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.927854617185876</v>
+        <v>9.46877167018857</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0330303701325935</v>
+        <v>0.4459203015066</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.105096317411007</v>
+        <v>0.420776537441113</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.417166003045904</v>
+        <v>-0.0180615081891665</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.0430162863581114</v>
+        <v>0.117821842832874</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.0173071712448539</v>
+        <v>0.323168738327668</v>
       </c>
       <c r="AG3" t="n">
-        <v>6.60630690069047</v>
+        <v>-0.669700687607101</v>
       </c>
       <c r="AH3" t="n">
-        <v>9.30332000354092</v>
+        <v>-0.0187544909375068</v>
       </c>
       <c r="AI3" t="n">
-        <v>-1.67825016003338</v>
+        <v>-1.8106182239334</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-1.64221588775254</v>
+        <v>0.674163136198667</v>
       </c>
       <c r="AK3" t="n">
-        <v>-1.97162814677493</v>
+        <v>-1.73679901150813</v>
       </c>
       <c r="AL3" t="n">
-        <v>-1.10435194077446</v>
+        <v>-0.479494709331329</v>
       </c>
       <c r="AM3" t="n">
-        <v>-15.3836596303792</v>
+        <v>-5.36789093780363</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.45206311539122</v>
+        <v>-0.0187544909375068</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.425281518186577</v>
+        <v>-0.00592210199875209</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.0134083555530665</v>
+        <v>-0.124514938626595</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.108622482127475</v>
+        <v>-0.0120689524286555</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.332117579665375</v>
+        <v>-0.0114778930171917</v>
       </c>
       <c r="AS3" t="n">
-        <v>-0.720902580572158</v>
+        <v>-0.00287469133994188</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>-0.0897801301390606</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>-0.430576864738703</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>-0.0400340885066818</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>-0.0210165998667944</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.00407273027768378</v>
+        <v>-0.0106117559266025</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.0410667121598777</v>
+        <v>0.00749715977048403</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.117450919779956</v>
+        <v>-0.0830287210732136</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.136368414944504</v>
+        <v>-0.1680946226619</v>
       </c>
       <c r="F4" t="n">
-        <v>0.132877420578937</v>
+        <v>0.199825540448243</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.0154027564737696</v>
+        <v>-0.0172861819723365</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.307119011858189</v>
+        <v>-0.275683944862422</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.548922495297754</v>
+        <v>-0.379057941144188</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.20183783684517</v>
+        <v>-0.204547004086075</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.118566933657541</v>
+        <v>-0.0833454461396008</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.0958881813966237</v>
+        <v>-0.0992528037685662</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.00253123638992195</v>
+        <v>-0.140513696688223</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.167941143656469</v>
+        <v>-0.0462313553754325</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0820742336547803</v>
+        <v>-0.0229236176192042</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.0263088790481869</v>
+        <v>-0.0790246509138639</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.109131310020982</v>
+        <v>-0.00663956893315173</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.00066193933376253</v>
+        <v>-0.193624134329541</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.189906071487923</v>
+        <v>-0.0727989321302532</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.104160559732293</v>
+        <v>-0.00177420639276151</v>
       </c>
       <c r="U4" t="n">
-        <v>0.039522361810215</v>
+        <v>-0.0096674549944769</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.0614718597661275</v>
+        <v>-0.0106117559266025</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.0464041859385657</v>
+        <v>0.238632907948636</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.0338404345255738</v>
+        <v>-0.0046582932973979</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.0182312559400307</v>
+        <v>-0.0321137235217982</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.238521113119427</v>
+        <v>-3.6567457814057</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0236436256690874</v>
+        <v>3.18733465096918</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0.0128545000856879</v>
+        <v>1.08531313865013</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.402057343736259</v>
+        <v>1.08471234170423</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.258378801029149</v>
+        <v>0.0374767126725199</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.11095311282397</v>
+        <v>1.69195356849872</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.0529335576495411</v>
+        <v>0.757185649293683</v>
       </c>
       <c r="AG4" t="n">
-        <v>-1.21157071622043</v>
+        <v>2.08283884722701</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.31687141436048</v>
+        <v>-0.0106117559266025</v>
       </c>
       <c r="AI4" t="n">
-        <v>-3.11703832031881</v>
+        <v>-4.33363206758846</v>
       </c>
       <c r="AJ4" t="n">
-        <v>5.41884447834923</v>
+        <v>3.47951944025571</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.210046541744577</v>
+        <v>-0.785465830641512</v>
       </c>
       <c r="AL4" t="n">
-        <v>-0.233624930212402</v>
+        <v>-1.42973298684114</v>
       </c>
       <c r="AM4" t="n">
-        <v>-0.660862273096854</v>
+        <v>-42.569701020505</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.07282164697012</v>
+        <v>-0.0106117559266025</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.07848557857878</v>
+        <v>0.0547550904069658</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.0221777860676539</v>
+        <v>-0.0652307468884785</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.69399121977064</v>
+        <v>-0.045505832365728</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.706960422741913</v>
+        <v>-0.0322047646995185</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.06371117645359</v>
+        <v>-0.0176792835525299</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0.270367223214788</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0.0992304648046233</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>-0.110769703093727</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>-0.0419005368711723</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.00673167299275149</v>
+        <v>-0.00827059132406005</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.0347292084641063</v>
+        <v>-0.122145398703835</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0328261720540513</v>
+        <v>-0.100353944929687</v>
       </c>
       <c r="E5" t="n">
-        <v>0.069640788279207</v>
+        <v>-0.111607999541908</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.23558743619847</v>
+        <v>-0.167499136732503</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0551491093403723</v>
+        <v>-0.0948922606611758</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0200773500729529</v>
+        <v>-0.0511182885771347</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0309151780414264</v>
+        <v>-0.13626796057704</v>
       </c>
       <c r="J5" t="n">
-        <v>0.00793243351758683</v>
+        <v>-0.050890800403464</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.0127429564067428</v>
+        <v>-0.0464039787783597</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.00746864012735139</v>
+        <v>-0.0271080966812821</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.00407177131554153</v>
+        <v>-0.0693706623716407</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0610725929330359</v>
+        <v>-0.0646861249494893</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0646190013655795</v>
+        <v>-0.028156383758068</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.0501813261660443</v>
+        <v>-0.0652895519420812</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.0627288273881337</v>
+        <v>-0.0949209647033602</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.0557910708914077</v>
+        <v>-0.0513093511877342</v>
       </c>
       <c r="S5" t="n">
-        <v>0.00714358329074641</v>
+        <v>-0.0663354354647752</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0652027839140039</v>
+        <v>0.0119601418619872</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0193108816561053</v>
+        <v>0.00632238022767996</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.0971004436853571</v>
+        <v>-0.00827059132406005</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.00985845655653883</v>
+        <v>-0.239717601334114</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.00981222271331742</v>
+        <v>-0.603345864949219</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.00710055982585504</v>
+        <v>0.0345324153460856</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.253417913076194</v>
+        <v>12.8766082668867</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.821984533914935</v>
+        <v>-0.185581204179267</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0570395588038852</v>
+        <v>-0.480762803947523</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.549165532607368</v>
+        <v>-0.491412281297821</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.918498051080108</v>
+        <v>-0.0204523238264708</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.123203624945622</v>
+        <v>-0.517328039756423</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.0366902980304318</v>
+        <v>-0.416990227244602</v>
       </c>
       <c r="AG5" t="n">
-        <v>14.5206568877922</v>
+        <v>-0.309598759212358</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.184740032180195</v>
+        <v>-0.00827059132406005</v>
       </c>
       <c r="AI5" t="n">
-        <v>-2.19668482282022</v>
+        <v>-3.29864109689281</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.196317820703139</v>
+        <v>0.0880140989518122</v>
       </c>
       <c r="AK5" t="n">
-        <v>-1.27387147322722</v>
+        <v>-1.32448945863975</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.134170559763075</v>
+        <v>-0.383079737175409</v>
       </c>
       <c r="AM5" t="n">
-        <v>-23.6733606084636</v>
+        <v>-6.34140711822642</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.47897297818923</v>
+        <v>-0.00827059132406005</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.489744137006237</v>
+        <v>-0.0126910136354993</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.0144008750482088</v>
+        <v>-0.0894390540455207</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.496845641090776</v>
+        <v>-0.0101994742962003</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.408232090007284</v>
+        <v>-0.0112512269908156</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0.19193106068152</v>
+        <v>0.0000448609568320835</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>-0.498559310609352</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>-0.805638210882072</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>-0.120809715617533</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>-0.0301455181868558</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B6" t="n">
-        <v>0.00555113639805628</v>
+        <v>0.00645129629028539</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0823461491472064</v>
+        <v>0.110530254099856</v>
       </c>
       <c r="D6" t="n">
-        <v>0.045756027977999</v>
+        <v>0.0575841815729827</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.268884610102412</v>
+        <v>0.0130683825400217</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0250732594075418</v>
+        <v>-0.0550287816600177</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0641327057226572</v>
+        <v>-0.00740902511946132</v>
       </c>
       <c r="H6" t="n">
-        <v>0.165057633260619</v>
+        <v>0.181416378387232</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0334163871646033</v>
+        <v>-0.0114937243976157</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0871373964874616</v>
+        <v>0.0849162728489249</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0617179253096211</v>
+        <v>0.0723233724184874</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0442360340276532</v>
+        <v>0.0583374781502086</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.000552838863278271</v>
+        <v>0.0598068556838989</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0195213076705624</v>
+        <v>-0.013714303297158</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0157424825911874</v>
+        <v>0.0977294767986963</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0520636525517499</v>
+        <v>0.0294017406603969</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.00781508506107168</v>
+        <v>-0.0126465291820841</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.0779164181796177</v>
+        <v>0.0700418218404284</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0779415575104651</v>
+        <v>0.0251407537430236</v>
       </c>
       <c r="T6" t="n">
-        <v>0.00337924006831701</v>
+        <v>0.0139718914512606</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0229519783821624</v>
+        <v>-0.000132894999783394</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.105754601435925</v>
+        <v>0.00645129629028539</v>
       </c>
       <c r="W6" t="n">
-        <v>0.00985438236746711</v>
+        <v>-0.0740218264774652</v>
       </c>
       <c r="X6" t="n">
-        <v>0.00588260237512417</v>
+        <v>-0.426109778443417</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0069717760779694</v>
+        <v>-0.00863925898046138</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.180905739035769</v>
+        <v>-2.62102808522828</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.766902240081742</v>
+        <v>-6.8923058608767</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.00374097397519409</v>
+        <v>0.137803941295357</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.130341917328592</v>
+        <v>0.136375350030841</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.217270617646816</v>
+        <v>-0.0151404486111813</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.038859456361763</v>
+        <v>-0.122453111385131</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.0279261970611694</v>
+        <v>-0.0227025532079354</v>
       </c>
       <c r="AG6" t="n">
-        <v>-3.05743373103904</v>
+        <v>-0.596281488285481</v>
       </c>
       <c r="AH6" t="n">
-        <v>-6.68984810457708</v>
+        <v>0.00645129629028539</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.270787095063621</v>
+        <v>0.645115029604612</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-3.80857704736126</v>
+        <v>-3.15401967973663</v>
       </c>
       <c r="AK6" t="n">
-        <v>-1.28757361530039</v>
+        <v>-0.479314393113188</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.736662978202032</v>
+        <v>0.611713139250937</v>
       </c>
       <c r="AM6" t="n">
-        <v>-16.4286426238764</v>
+        <v>-16.3729940487149</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.131556766629287</v>
+        <v>0.00645129629028539</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.131451976361691</v>
+        <v>-0.0145101640738114</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.0097694063342077</v>
+        <v>-0.0878933964847373</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.12588758098753</v>
+        <v>0.00932060029867682</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.0321582264122215</v>
+        <v>0.00381549939108643</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0.528393115614066</v>
+        <v>0.00806407023915974</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0.0874724920290433</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>-0.190520132930576</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0.0388849601319051</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.011774904127128</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0063459833092419</v>
+        <v>0.00814176389116344</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0762510972787558</v>
+        <v>0.0566896115469599</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0951238890839605</v>
+        <v>0.0606679378029226</v>
       </c>
       <c r="E7" t="n">
-        <v>0.44574553885194</v>
+        <v>0.249091669555361</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0574075808339198</v>
+        <v>0.0666871890806187</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0916417841492091</v>
+        <v>0.0925814739476112</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0617300743368635</v>
+        <v>0.0621870358794253</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0222189097171767</v>
+        <v>-0.18730374035732</v>
       </c>
       <c r="J7" t="n">
-        <v>0.101508703713092</v>
+        <v>0.0401154080248118</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0993621069949495</v>
+        <v>0.104051826227268</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00637475582883116</v>
+        <v>0.00216231281318766</v>
       </c>
       <c r="M7" t="n">
-        <v>0.00359376924725762</v>
+        <v>0.0881885399743659</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0685871124731934</v>
+        <v>0.110201493013319</v>
       </c>
       <c r="O7" t="n">
-        <v>0.121776069366707</v>
+        <v>0.0233785732097411</v>
       </c>
       <c r="P7" t="n">
-        <v>0.050302152866095</v>
+        <v>0.105081635983518</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.111682514484188</v>
+        <v>0.0959233290497806</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0866975566900409</v>
+        <v>0.0377582789716094</v>
       </c>
       <c r="S7" t="n">
-        <v>0.106618360799044</v>
+        <v>0.110974802955842</v>
       </c>
       <c r="T7" t="n">
-        <v>0.116402140518365</v>
+        <v>-0.000876495039657422</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0324931498419894</v>
+        <v>-0.00620743716453717</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.134920154694001</v>
+        <v>0.00814176389116344</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.0288868643896365</v>
+        <v>-0.283340517880106</v>
       </c>
       <c r="X7" t="n">
-        <v>0.034787235558065</v>
+        <v>0.138975754240142</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0131586497191799</v>
+        <v>-0.00159461831557265</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.384735367944911</v>
+        <v>-4.9668067447289</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.141025226132511</v>
+        <v>-7.22304860551217</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.000977976392527129</v>
+        <v>0.417680620231473</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.38351694021484</v>
+        <v>0.423753622457581</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.609092399827871</v>
+        <v>-0.00435850361499742</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.103702598697388</v>
+        <v>0.288568308229093</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.0416582559253902</v>
+        <v>0.158753315312689</v>
       </c>
       <c r="AG7" t="n">
-        <v>-4.96371931322526</v>
+        <v>0.197079987747135</v>
       </c>
       <c r="AH7" t="n">
-        <v>-6.91887607772875</v>
+        <v>0.00814176389116344</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.835743738101553</v>
+        <v>1.13742322544659</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-4.81695533409936</v>
+        <v>-5.9815866905914</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.20945284264749</v>
+        <v>2.17142306102353</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.5234842265337</v>
+        <v>1.55919121343083</v>
       </c>
       <c r="AM7" t="n">
-        <v>-16.8346465815068</v>
+        <v>-32.8114717861355</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.416042465184197</v>
+        <v>0.00814176389116344</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.42220934571956</v>
+        <v>-0.0488867604947774</v>
       </c>
       <c r="AP7" t="n">
-        <v>-0.00182672583321153</v>
+        <v>-0.130889359225575</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.289811455373398</v>
+        <v>-0.0270952994673804</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.156234646444245</v>
+        <v>0.036756012010565</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.257129890884577</v>
+        <v>0.0264964849976002</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0.356836304294275</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>-0.56377954951785</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>-0.106160778920502</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>-0.0501658689365992</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0456177585177844</v>
+        <v>0.0510175523324224</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.0955237738693273</v>
+        <v>-0.137628253973861</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0912897764735067</v>
+        <v>-0.108026756717855</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.168841549380056</v>
+        <v>-0.115276776801663</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0369322431845286</v>
+        <v>-0.0227177683600649</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.107676702018946</v>
+        <v>-0.0504494845433958</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0387327729918419</v>
+        <v>-0.090358557590661</v>
       </c>
       <c r="I8" t="n">
-        <v>0.231440075369165</v>
+        <v>0.312408160364022</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.00033356703397456</v>
+        <v>0.0577138464575576</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.0409767345341007</v>
+        <v>-0.0719286596465708</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0534166451664165</v>
+        <v>-0.0461500300845078</v>
       </c>
       <c r="M8" t="n">
-        <v>0.00144313282934757</v>
+        <v>0.0117997451904834</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0432650670743699</v>
+        <v>0.085005532500854</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0862089139828309</v>
+        <v>0.262537333867658</v>
       </c>
       <c r="P8" t="n">
-        <v>0.289375773862038</v>
+        <v>0.0812860850993163</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.106116795912135</v>
+        <v>-0.0435412411731385</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.109773235544435</v>
+        <v>0.076758094836057</v>
       </c>
       <c r="S8" t="n">
-        <v>0.00328032350627723</v>
+        <v>0.0905617445971902</v>
       </c>
       <c r="T8" t="n">
-        <v>0.116078902248866</v>
+        <v>-0.00209657549514964</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.000427092912728223</v>
+        <v>-0.00677780817797705</v>
       </c>
       <c r="V8" t="n">
-        <v>0.603390467357332</v>
+        <v>0.0510175523324224</v>
       </c>
       <c r="W8" t="n">
-        <v>0.131047600709987</v>
+        <v>-0.0179969006256854</v>
       </c>
       <c r="X8" t="n">
-        <v>0.016454147776501</v>
+        <v>1.72478003474691</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.00758748755428124</v>
+        <v>0.0323052094194796</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0.0463657948547163</v>
+        <v>-8.95649637019016</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.26735397475303</v>
+        <v>-16.3473555096506</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0230202234630654</v>
+        <v>-1.96231738904952</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.468430059138016</v>
+        <v>-1.89565515953533</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.72189026612669</v>
+        <v>-0.0229033995739873</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.33367196740454</v>
+        <v>-1.89738612961306</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.108910061002259</v>
+        <v>-1.22631104841774</v>
       </c>
       <c r="AG8" t="n">
-        <v>-17.5407433415457</v>
+        <v>-0.81200803808392</v>
       </c>
       <c r="AH8" t="n">
-        <v>-15.91730656648</v>
+        <v>0.0510175523324224</v>
       </c>
       <c r="AI8" t="n">
-        <v>8.45418315083766</v>
+        <v>11.114539057225</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-5.88535655505327</v>
+        <v>-8.1921204196342</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.2195301986862</v>
+        <v>1.91725271712848</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.55604206594151</v>
+        <v>1.2301571278282</v>
       </c>
       <c r="AM8" t="n">
-        <v>-25.1257050387664</v>
+        <v>-14.5716415236272</v>
       </c>
       <c r="AN8" t="n">
-        <v>-1.96632816405502</v>
+        <v>0.0510175523324224</v>
       </c>
       <c r="AO8" t="n">
-        <v>-1.90110008752257</v>
+        <v>0.0070596788647981</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0.0150055734726078</v>
+        <v>0.623298285383439</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-1.88335741914045</v>
+        <v>0.126299451263104</v>
       </c>
       <c r="AR8" t="n">
-        <v>-1.19310898265885</v>
+        <v>0.0144864590925036</v>
       </c>
       <c r="AS8" t="n">
-        <v>-0.769000914835182</v>
+        <v>-0.00241545656382177</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>-0.364200052676681</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0.868272419517312</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0.332533194885255</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0.103441942041893</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.0168211114768003</v>
+        <v>-0.0165178602451828</v>
       </c>
       <c r="C9" t="n">
-        <v>0.109642058477056</v>
+        <v>0.0689154261727211</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0282187554247852</v>
+        <v>0.0331875706513305</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0793063074925628</v>
+        <v>0.148720027483957</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0712631776822777</v>
+        <v>-0.00976139819069165</v>
       </c>
       <c r="G9" t="n">
-        <v>0.112146464743869</v>
+        <v>0.0856558050038556</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0569534450988202</v>
+        <v>0.0508762586951877</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.281463352574371</v>
+        <v>-0.207119473504056</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0597768551696921</v>
+        <v>0.0997779287838945</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0719101164429058</v>
+        <v>0.0677606001373833</v>
       </c>
       <c r="L9" t="n">
-        <v>0.00457360058260213</v>
+        <v>-0.0108889277572815</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.000789914491348854</v>
+        <v>0.0795451746591995</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0357822598475839</v>
+        <v>0.0415196753667928</v>
       </c>
       <c r="O9" t="n">
-        <v>0.037592421822653</v>
+        <v>-0.032506100395022</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.0262296068434413</v>
+        <v>0.0384087800046429</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0318627401022921</v>
+        <v>0.0907601859969603</v>
       </c>
       <c r="R9" t="n">
-        <v>0.119153171558655</v>
+        <v>0.105994356142494</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0597801320685628</v>
+        <v>0.0417863572476073</v>
       </c>
       <c r="T9" t="n">
-        <v>0.032911930721582</v>
+        <v>-0.000853934485337494</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0114423095936808</v>
+        <v>-0.00619126760761209</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.0906207301447358</v>
+        <v>-0.0165178602451828</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.0375635643111969</v>
+        <v>0.117661170908875</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.0080701761737479</v>
+        <v>-0.316776579339672</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.00844121886105549</v>
+        <v>-0.0560367343376188</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.190948752183545</v>
+        <v>-0.642977014608471</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.407754800119376</v>
+        <v>24.8075123968551</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0.0503048362851284</v>
+        <v>1.05843136508607</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.0130802703554556</v>
+        <v>1.06447099286481</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0.57875202427035</v>
+        <v>-0.00394236784617542</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.0682036469998466</v>
+        <v>0.786101660215013</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.0529060281662314</v>
+        <v>0.697507361040615</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.2787501340112</v>
+        <v>-0.0378910393975687</v>
       </c>
       <c r="AH9" t="n">
-        <v>24.2613315013326</v>
+        <v>-0.0165178602451828</v>
       </c>
       <c r="AI9" t="n">
-        <v>-1.32011445384071</v>
+        <v>-1.66707982254063</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.01596808470018</v>
+        <v>-0.0627951798163674</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.481498943211425</v>
+        <v>-0.202045598243233</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.765028468380654</v>
+        <v>-0.343026876426291</v>
       </c>
       <c r="AM9" t="n">
-        <v>-14.5740700255864</v>
+        <v>-38.8813346529616</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.05053763541828</v>
+        <v>-0.0165178602451828</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.05844144209026</v>
+        <v>-0.0311334277035191</v>
       </c>
       <c r="AP9" t="n">
-        <v>-0.00446654054991485</v>
+        <v>-0.085991106624436</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.773940374986102</v>
+        <v>-0.0372883416236204</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.67522791821448</v>
+        <v>-0.00671792788632267</v>
       </c>
       <c r="AS9" t="n">
-        <v>-0.0332216895996657</v>
+        <v>0.00187555546266787</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>-0.0201674683720062</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>-0.560270477376811</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>-0.065809910687646</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>-0.0495860187344967</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.0113921441123039</v>
+        <v>-0.0126666021447166</v>
       </c>
       <c r="C10" t="n">
-        <v>0.139404051619802</v>
+        <v>0.194779164660011</v>
       </c>
       <c r="D10" t="n">
-        <v>0.107285332965643</v>
+        <v>0.0993104454721675</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.068823900814924</v>
+        <v>0.0135457836029183</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0938871034456687</v>
+        <v>0.0695540564260492</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0466774006868071</v>
+        <v>0.0717473776606122</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0738381780311957</v>
+        <v>0.085485526010238</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0387296815907503</v>
+        <v>0.0605231060707927</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0606859536316434</v>
+        <v>0.0284851829426533</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0893699838372815</v>
+        <v>0.108520269425552</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0595331309851177</v>
+        <v>0.066004582978239</v>
       </c>
       <c r="M10" t="n">
-        <v>0.00063956423728254</v>
+        <v>0.00746375529460798</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.00642399961670328</v>
+        <v>0.0313466518171351</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0386621917296251</v>
+        <v>-0.0503840278774361</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.0475481829439271</v>
+        <v>0.0330187295212955</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0352258020508416</v>
+        <v>0.0651300598910512</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0382133994050293</v>
+        <v>0.0209693744345587</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0598813946163501</v>
+        <v>0.0279753954941065</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0307297191984839</v>
+        <v>-0.00494730670772397</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0227375876793535</v>
+        <v>-0.0059363948616229</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.0661480202177824</v>
+        <v>-0.0126666021447166</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.0200532932339702</v>
+        <v>-0.034254738347036</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.00707110008855124</v>
+        <v>-0.318820967683793</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.00120523268413109</v>
+        <v>0.00288103584039171</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.0239032212709713</v>
+        <v>9.18313302274477</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.394690486995836</v>
+        <v>2.60604523920295</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.00212402519970797</v>
+        <v>0.0993920276010099</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.247596879583328</v>
+        <v>0.0649110900285878</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.352871039403625</v>
+        <v>-0.00601580844399689</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.10532785656265</v>
+        <v>0.121246255656583</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.0134245747644612</v>
+        <v>0.0824696836727371</v>
       </c>
       <c r="AG10" t="n">
-        <v>11.2478155301854</v>
+        <v>0.324413975954479</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.39957058857554</v>
+        <v>-0.0126666021447166</v>
       </c>
       <c r="AI10" t="n">
-        <v>-2.52870047392549</v>
+        <v>-3.3738464829268</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.417847332174012</v>
+        <v>0.109681635244063</v>
       </c>
       <c r="AK10" t="n">
-        <v>-0.461410484372147</v>
+        <v>-1.06939568123992</v>
       </c>
       <c r="AL10" t="n">
-        <v>-0.511349128480068</v>
+        <v>-0.97502565826004</v>
       </c>
       <c r="AM10" t="n">
-        <v>7.64676420545428</v>
+        <v>20.6358648362426</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.0815159276062689</v>
+        <v>-0.0126666021447166</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.0447517134776636</v>
+        <v>0.0162128674262684</v>
       </c>
       <c r="AP10" t="n">
-        <v>-0.00623502071725324</v>
+        <v>-0.0685088524170304</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.0872606092596328</v>
+        <v>-0.0184782945022104</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.0760202740505429</v>
+        <v>-0.00562302260810126</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.220337792447717</v>
+        <v>-0.00229376249545885</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0.226312930238288</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0.25487024586806</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>-0.106321546072497</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0.000659318827429851</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.00471042328172969</v>
+        <v>-0.00347800705486099</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0160381593779067</v>
+        <v>0.149352779194863</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0248026151646159</v>
+        <v>0.0880352012824857</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.121111601409691</v>
+        <v>-0.0634347530437051</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0286239084157839</v>
+        <v>0.0560046025212957</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0078439657200221</v>
+        <v>0.031015978669683</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.095293669995948</v>
+        <v>0.0177639160519283</v>
       </c>
       <c r="I11" t="n">
-        <v>0.551529544599941</v>
+        <v>0.308377868489366</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.0659412140566147</v>
+        <v>-0.0424987960969301</v>
       </c>
       <c r="K11" t="n">
-        <v>0.00121775774629363</v>
+        <v>0.0476275339089251</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0611701402851368</v>
+        <v>0.110736216830027</v>
       </c>
       <c r="M11" t="n">
-        <v>0.000805397541165776</v>
+        <v>0.0434747956825235</v>
       </c>
       <c r="N11" t="n">
-        <v>0.045845814186503</v>
+        <v>0.0214079457966792</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0323107042167563</v>
+        <v>-0.0430517030745228</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.0520580043306554</v>
+        <v>0.0336816977502262</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.0271864790902579</v>
+        <v>0.0252286220488428</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.0041608521600098</v>
+        <v>-0.050256298002095</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.061880572675543</v>
+        <v>0.0237553759118981</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0220850558744589</v>
+        <v>0.0161860205464844</v>
       </c>
       <c r="U11" t="n">
-        <v>0.00665614595998485</v>
+        <v>0.0534106065636256</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.0942585371644368</v>
+        <v>-0.00347800705486099</v>
       </c>
       <c r="W11" t="n">
-        <v>0.00665094210236605</v>
+        <v>-0.0356350520085281</v>
       </c>
       <c r="X11" t="n">
-        <v>0.0306973186000781</v>
+        <v>0.130356101422482</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.0178277003423856</v>
+        <v>-0.0171102899495</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.00988591908696108</v>
+        <v>6.46159713625299</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.389825896246746</v>
+        <v>-3.79001194417842</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0.0243453841320599</v>
+        <v>-0.280277339731389</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.000849929131478161</v>
+        <v>-0.315375631341959</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.46115965373385</v>
+        <v>-0.01606426181088</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.00770263719203381</v>
+        <v>-0.268974540442095</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.0287831104043255</v>
+        <v>-0.198117667048756</v>
       </c>
       <c r="AG11" t="n">
-        <v>8.54147204112823</v>
+        <v>-0.485241215412147</v>
       </c>
       <c r="AH11" t="n">
-        <v>-3.81903947977955</v>
+        <v>-0.00347800705486099</v>
       </c>
       <c r="AI11" t="n">
-        <v>-1.1308740132949</v>
+        <v>-1.43196146583946</v>
       </c>
       <c r="AJ11" t="n">
-        <v>4.54087222227513</v>
+        <v>5.93171983273495</v>
       </c>
       <c r="AK11" t="n">
-        <v>-0.718411958907107</v>
+        <v>-0.906522357558994</v>
       </c>
       <c r="AL11" t="n">
-        <v>-0.990437269736089</v>
+        <v>-0.824336869597266</v>
       </c>
       <c r="AM11" t="n">
-        <v>45.2544335212494</v>
+        <v>65.2698455856311</v>
       </c>
       <c r="AN11" t="n">
-        <v>-0.275047516961716</v>
+        <v>-0.00347800705486099</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.312829094390601</v>
+        <v>0.00419728519968035</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.014057749278441</v>
+        <v>-0.0794655684818871</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.274334732025035</v>
+        <v>0.00781679675748731</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0.182527166770818</v>
+        <v>0.0287309003037915</v>
       </c>
       <c r="AS11" t="n">
-        <v>-0.555892790954916</v>
+        <v>0.00568403486323562</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0.134164225856</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0.48231177072471</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>-0.00973001332228931</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.0317574067545379</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0235404779913371</v>
+        <v>0.0290340072791658</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0326243399727903</v>
+        <v>0.062447825070159</v>
       </c>
       <c r="D12" t="n">
-        <v>0.115948268785888</v>
+        <v>0.168512822275015</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.168703646000245</v>
+        <v>-0.0451106247733537</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0197265264805468</v>
+        <v>0.0346536432378397</v>
       </c>
       <c r="G12" t="n">
-        <v>0.107496305924837</v>
+        <v>0.0657380702100631</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0955977257721718</v>
+        <v>0.120078491797855</v>
       </c>
       <c r="I12" t="n">
-        <v>0.378360474213755</v>
+        <v>0.466917790334461</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.0638406601284575</v>
+        <v>0.0131584596459581</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0554692159586531</v>
+        <v>0.052887700524395</v>
       </c>
       <c r="L12" t="n">
-        <v>0.117582768484844</v>
+        <v>0.131963140598635</v>
       </c>
       <c r="M12" t="n">
-        <v>0.00339290303799786</v>
+        <v>0.194140314964401</v>
       </c>
       <c r="N12" t="n">
-        <v>0.343698976117358</v>
+        <v>0.0566276373827611</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0805762771722767</v>
+        <v>-0.00226384493916054</v>
       </c>
       <c r="P12" t="n">
-        <v>0.00513272834805548</v>
+        <v>0.093276677117938</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.135007930855558</v>
+        <v>0.0497909447038726</v>
       </c>
       <c r="R12" t="n">
-        <v>0.103606709087854</v>
+        <v>-0.00079319975934629</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0827074190977706</v>
+        <v>0.0845725423401366</v>
       </c>
       <c r="T12" t="n">
-        <v>0.12984336078085</v>
+        <v>-0.0158064113019022</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0250388428288297</v>
+        <v>-0.00992309874196714</v>
       </c>
       <c r="V12" t="n">
-        <v>0.133432882910471</v>
+        <v>0.0290340072791658</v>
       </c>
       <c r="W12" t="n">
-        <v>0.0322082278331423</v>
+        <v>0.102569215250328</v>
       </c>
       <c r="X12" t="n">
-        <v>0.0286395333477049</v>
+        <v>1.02881316815924</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.00650785355391768</v>
+        <v>0.0251369998132533</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.197239782221858</v>
+        <v>10.4443502682577</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.3304363502701</v>
+        <v>-11.8150048192469</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0.00733753655321984</v>
+        <v>-1.96199186569072</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.282490433363905</v>
+        <v>-1.8949825304987</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.28121780712863</v>
+        <v>-0.0242905439731241</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.198859392204019</v>
+        <v>-1.59590615976577</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.0656741064335221</v>
+        <v>-1.22759840189505</v>
       </c>
       <c r="AG12" t="n">
-        <v>7.74413971627881</v>
+        <v>-1.3537273060739</v>
       </c>
       <c r="AH12" t="n">
-        <v>-11.4170718261203</v>
+        <v>0.0290340072791658</v>
       </c>
       <c r="AI12" t="n">
-        <v>3.21126521176371</v>
+        <v>4.26920532369115</v>
       </c>
       <c r="AJ12" t="n">
-        <v>7.07944860135927</v>
+        <v>6.78588885711216</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.50333314202722</v>
+        <v>3.26215139466083</v>
       </c>
       <c r="AL12" t="n">
-        <v>-0.313195818781744</v>
+        <v>1.15774783364925</v>
       </c>
       <c r="AM12" t="n">
-        <v>71.2557777668424</v>
+        <v>70.4542453034088</v>
       </c>
       <c r="AN12" t="n">
-        <v>-1.90354976202227</v>
+        <v>0.0290340072791658</v>
       </c>
       <c r="AO12" t="n">
-        <v>-1.83424584012168</v>
+        <v>-0.0156950042196849</v>
       </c>
       <c r="AP12" t="n">
-        <v>-0.016032097575927</v>
+        <v>0.0503504948466361</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-1.55777189055532</v>
+        <v>0.0319092339051696</v>
       </c>
       <c r="AR12" t="n">
-        <v>-1.18979736034696</v>
+        <v>0.0302245199374329</v>
       </c>
       <c r="AS12" t="n">
-        <v>-1.40355896678411</v>
+        <v>0.00599980181313706</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0.283915495752221</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1.25725739989224</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0.198453286570986</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0.0695752226753227</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.0177102085353778</v>
+        <v>-0.022420261701553</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.246071702285308</v>
+        <v>-0.331401409305866</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.161479202948137</v>
+        <v>-0.162619848384915</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.028238800497958</v>
+        <v>-0.0562945592106302</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0713935973717869</v>
+        <v>-0.111160248985662</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.113817679776257</v>
+        <v>-0.133967244021868</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.190584151980672</v>
+        <v>-0.237330111423642</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.138594609224981</v>
+        <v>-0.166672451259877</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.136257270808377</v>
+        <v>-0.162472982728464</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.143401529831563</v>
+        <v>-0.181810665424119</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.111099626004602</v>
+        <v>-0.123861185506901</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.00579098178559572</v>
+        <v>-0.185809366904684</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.215114474632891</v>
+        <v>-0.115351183083685</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.139225287492605</v>
+        <v>-0.145420703633541</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.148097154703746</v>
+        <v>-0.171976078222491</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.188520661258403</v>
+        <v>-0.127784997055915</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.101525500954997</v>
+        <v>-0.151355170842901</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.129790769086983</v>
+        <v>-0.168424724444471</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.185495319299347</v>
+        <v>-0.00310887118567709</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0330916944608763</v>
+        <v>-0.0104389664730564</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.0143204856864917</v>
+        <v>-0.022420261701553</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.0405986199306555</v>
+        <v>0.0996129393258328</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.035335622748763</v>
+        <v>-0.636789414539381</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0.0181122288317814</v>
+        <v>-0.000535905416495116</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.0882303468880453</v>
+        <v>-8.92496448610394</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.988326863778314</v>
+        <v>10.5679640030331</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0.00549979939322641</v>
+        <v>1.0654007533225</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.127657445341387</v>
+        <v>1.04508319890403</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0.466262947311433</v>
+        <v>0.104684631324917</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0.11095311282397</v>
+        <v>1.24391823479601</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.0306133553077001</v>
+        <v>0.837362146580173</v>
       </c>
       <c r="AG13" t="n">
-        <v>-8.38785422331802</v>
+        <v>1.87034141716541</v>
       </c>
       <c r="AH13" t="n">
-        <v>10.1684767858166</v>
+        <v>-0.022420261701553</v>
       </c>
       <c r="AI13" t="n">
-        <v>-2.47398315798306</v>
+        <v>-3.69809949426058</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.69036107171225</v>
+        <v>2.40170986082051</v>
       </c>
       <c r="AK13" t="n">
-        <v>-0.335748960393798</v>
+        <v>-0.699027958914593</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.108536161006829</v>
+        <v>-0.594911104085817</v>
       </c>
       <c r="AM13" t="n">
-        <v>-5.79021799987349</v>
+        <v>-10.8398832885408</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.03638537303023</v>
+        <v>-0.022420261701553</v>
       </c>
       <c r="AO13" t="n">
-        <v>1.01625616481922</v>
+        <v>0.0235227963443035</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.0813273935329366</v>
+        <v>-0.0129243837296623</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.2330314252836</v>
+        <v>-0.0411016566401093</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.80340033715442</v>
+        <v>-0.0332452111152857</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.87381409570513</v>
+        <v>-0.0110944784640508</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>-0.149526899565437</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>-0.513702335853815</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>-0.111200809177955</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>-0.034822419453474</v>
       </c>
     </row>
   </sheetData>

--- a/sum.var_AMR_ES_C3G_R.xlsx
+++ b/sum.var_AMR_ES_C3G_R.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -69,6 +69,9 @@
   </si>
   <si>
     <t xml:space="preserve">log_AMC_ville_tot_except_FQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prescri_1</t>
   </si>
   <si>
     <t xml:space="preserve">AMR_animaux_production_C3G_R</t>
@@ -671,10 +674,13 @@
       <c r="AW1" t="s">
         <v>48</v>
       </c>
+      <c r="AX1" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B2" t="n">
         <v>-0.00192505045855437</v>
@@ -731,99 +737,102 @@
         <v>-0.115022957316709</v>
       </c>
       <c r="T2" t="n">
+        <v>0.0780895994364895</v>
+      </c>
+      <c r="U2" t="n">
         <v>-0.0061525067524421</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>-0.0110027515557436</v>
       </c>
-      <c r="V2" t="n">
+      <c r="W2" t="n">
         <v>-0.00192505045855437</v>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>0.153022366111796</v>
       </c>
-      <c r="X2" t="n">
+      <c r="Y2" t="n">
         <v>0.0572789883436409</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>-0.013401295858147</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AA2" t="n">
         <v>-12.3491190226778</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AB2" t="n">
         <v>-4.38432001660486</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AC2" t="n">
         <v>0.375407250726009</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AD2" t="n">
         <v>0.357342469242618</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AE2" t="n">
         <v>-0.0109321781074568</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AF2" t="n">
         <v>0.152438110734191</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AG2" t="n">
         <v>0.235273003586518</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AH2" t="n">
         <v>-0.210225694021555</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AI2" t="n">
         <v>-0.00192505045855437</v>
       </c>
-      <c r="AI2" t="n">
+      <c r="AJ2" t="n">
         <v>2.44759601801482</v>
       </c>
-      <c r="AJ2" t="n">
+      <c r="AK2" t="n">
         <v>-2.0801748915393</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AL2" t="n">
         <v>-0.147766882953508</v>
       </c>
-      <c r="AL2" t="n">
+      <c r="AM2" t="n">
         <v>0.470798627558077</v>
       </c>
-      <c r="AM2" t="n">
+      <c r="AN2" t="n">
         <v>11.3963686512327</v>
       </c>
-      <c r="AN2" t="n">
+      <c r="AO2" t="n">
         <v>-0.00192505045855437</v>
       </c>
-      <c r="AO2" t="n">
+      <c r="AP2" t="n">
         <v>0.0230907538840277</v>
       </c>
-      <c r="AP2" t="n">
+      <c r="AQ2" t="n">
         <v>0.0712086262938508</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AR2" t="n">
         <v>0.016391769099467</v>
       </c>
-      <c r="AR2" t="n">
+      <c r="AS2" t="n">
         <v>-0.0134933444181438</v>
       </c>
-      <c r="AS2" t="n">
+      <c r="AT2" t="n">
         <v>-0.0118071359168294</v>
       </c>
-      <c r="AT2" t="n">
+      <c r="AU2" t="n">
         <v>-0.236834810022079</v>
       </c>
-      <c r="AU2" t="n">
+      <c r="AV2" t="n">
         <v>0.102545270492877</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="AW2" t="n">
         <v>0.100965123810685</v>
       </c>
-      <c r="AW2" t="n">
+      <c r="AX2" t="n">
         <v>0.0104281676230812</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B3" t="n">
         <v>-0.0187544909375068</v>
@@ -880,99 +889,102 @@
         <v>0.0178150770664027</v>
       </c>
       <c r="T3" t="n">
+        <v>-0.03304366966862</v>
+      </c>
+      <c r="U3" t="n">
         <v>-0.00650174649908075</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>0.00654508778547107</v>
       </c>
-      <c r="V3" t="n">
+      <c r="W3" t="n">
         <v>-0.0187544909375068</v>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>-0.0265319628725331</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Y3" t="n">
         <v>-0.773703148659539</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>0.0345761659603827</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AA3" t="n">
         <v>3.15244881080114</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AB3" t="n">
         <v>9.46877167018857</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AC3" t="n">
         <v>0.4459203015066</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AD3" t="n">
         <v>0.420776537441113</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AE3" t="n">
         <v>-0.0180615081891665</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AF3" t="n">
         <v>0.117821842832874</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AG3" t="n">
         <v>0.323168738327668</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AH3" t="n">
         <v>-0.669700687607101</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AI3" t="n">
         <v>-0.0187544909375068</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AJ3" t="n">
         <v>-1.8106182239334</v>
       </c>
-      <c r="AJ3" t="n">
+      <c r="AK3" t="n">
         <v>0.674163136198667</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AL3" t="n">
         <v>-1.73679901150813</v>
       </c>
-      <c r="AL3" t="n">
+      <c r="AM3" t="n">
         <v>-0.479494709331329</v>
       </c>
-      <c r="AM3" t="n">
+      <c r="AN3" t="n">
         <v>-5.36789093780363</v>
       </c>
-      <c r="AN3" t="n">
+      <c r="AO3" t="n">
         <v>-0.0187544909375068</v>
       </c>
-      <c r="AO3" t="n">
+      <c r="AP3" t="n">
         <v>-0.00592210199875209</v>
       </c>
-      <c r="AP3" t="n">
+      <c r="AQ3" t="n">
         <v>-0.124514938626595</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AR3" t="n">
         <v>-0.0120689524286555</v>
       </c>
-      <c r="AR3" t="n">
+      <c r="AS3" t="n">
         <v>-0.0114778930171917</v>
       </c>
-      <c r="AS3" t="n">
+      <c r="AT3" t="n">
         <v>-0.00287469133994188</v>
       </c>
-      <c r="AT3" t="n">
+      <c r="AU3" t="n">
         <v>-0.0897801301390606</v>
       </c>
-      <c r="AU3" t="n">
+      <c r="AV3" t="n">
         <v>-0.430576864738703</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="AW3" t="n">
         <v>-0.0400340885066818</v>
       </c>
-      <c r="AW3" t="n">
+      <c r="AX3" t="n">
         <v>-0.0210165998667944</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B4" t="n">
         <v>-0.0106117559266025</v>
@@ -1029,99 +1041,102 @@
         <v>-0.0727989321302532</v>
       </c>
       <c r="T4" t="n">
+        <v>0.115921893157811</v>
+      </c>
+      <c r="U4" t="n">
         <v>-0.00177420639276151</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>-0.0096674549944769</v>
       </c>
-      <c r="V4" t="n">
+      <c r="W4" t="n">
         <v>-0.0106117559266025</v>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>0.238632907948636</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Y4" t="n">
         <v>-0.0046582932973979</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>-0.0321137235217982</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AA4" t="n">
         <v>-3.6567457814057</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AB4" t="n">
         <v>3.18733465096918</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AC4" t="n">
         <v>1.08531313865013</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AD4" t="n">
         <v>1.08471234170423</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AE4" t="n">
         <v>0.0374767126725199</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AF4" t="n">
         <v>1.69195356849872</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AG4" t="n">
         <v>0.757185649293683</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AH4" t="n">
         <v>2.08283884722701</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AI4" t="n">
         <v>-0.0106117559266025</v>
       </c>
-      <c r="AI4" t="n">
+      <c r="AJ4" t="n">
         <v>-4.33363206758846</v>
       </c>
-      <c r="AJ4" t="n">
+      <c r="AK4" t="n">
         <v>3.47951944025571</v>
       </c>
-      <c r="AK4" t="n">
+      <c r="AL4" t="n">
         <v>-0.785465830641512</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="AM4" t="n">
         <v>-1.42973298684114</v>
       </c>
-      <c r="AM4" t="n">
+      <c r="AN4" t="n">
         <v>-42.569701020505</v>
       </c>
-      <c r="AN4" t="n">
+      <c r="AO4" t="n">
         <v>-0.0106117559266025</v>
       </c>
-      <c r="AO4" t="n">
+      <c r="AP4" t="n">
         <v>0.0547550904069658</v>
       </c>
-      <c r="AP4" t="n">
+      <c r="AQ4" t="n">
         <v>-0.0652307468884785</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AR4" t="n">
         <v>-0.045505832365728</v>
       </c>
-      <c r="AR4" t="n">
+      <c r="AS4" t="n">
         <v>-0.0322047646995185</v>
       </c>
-      <c r="AS4" t="n">
+      <c r="AT4" t="n">
         <v>-0.0176792835525299</v>
       </c>
-      <c r="AT4" t="n">
+      <c r="AU4" t="n">
         <v>0.270367223214788</v>
       </c>
-      <c r="AU4" t="n">
+      <c r="AV4" t="n">
         <v>0.0992304648046233</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="AW4" t="n">
         <v>-0.110769703093727</v>
       </c>
-      <c r="AW4" t="n">
+      <c r="AX4" t="n">
         <v>-0.0419005368711723</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B5" t="n">
         <v>-0.00827059132406005</v>
@@ -1178,99 +1193,102 @@
         <v>-0.0663354354647752</v>
       </c>
       <c r="T5" t="n">
+        <v>0.0305634704180892</v>
+      </c>
+      <c r="U5" t="n">
         <v>0.0119601418619872</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>0.00632238022767996</v>
       </c>
-      <c r="V5" t="n">
+      <c r="W5" t="n">
         <v>-0.00827059132406005</v>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>-0.239717601334114</v>
       </c>
-      <c r="X5" t="n">
+      <c r="Y5" t="n">
         <v>-0.603345864949219</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>0.0345324153460856</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AA5" t="n">
         <v>12.8766082668867</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AB5" t="n">
         <v>-0.185581204179267</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AC5" t="n">
         <v>-0.480762803947523</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AD5" t="n">
         <v>-0.491412281297821</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AE5" t="n">
         <v>-0.0204523238264708</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AF5" t="n">
         <v>-0.517328039756423</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AG5" t="n">
         <v>-0.416990227244602</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AH5" t="n">
         <v>-0.309598759212358</v>
       </c>
-      <c r="AH5" t="n">
+      <c r="AI5" t="n">
         <v>-0.00827059132406005</v>
       </c>
-      <c r="AI5" t="n">
+      <c r="AJ5" t="n">
         <v>-3.29864109689281</v>
       </c>
-      <c r="AJ5" t="n">
+      <c r="AK5" t="n">
         <v>0.0880140989518122</v>
       </c>
-      <c r="AK5" t="n">
+      <c r="AL5" t="n">
         <v>-1.32448945863975</v>
       </c>
-      <c r="AL5" t="n">
+      <c r="AM5" t="n">
         <v>-0.383079737175409</v>
       </c>
-      <c r="AM5" t="n">
+      <c r="AN5" t="n">
         <v>-6.34140711822642</v>
       </c>
-      <c r="AN5" t="n">
+      <c r="AO5" t="n">
         <v>-0.00827059132406005</v>
       </c>
-      <c r="AO5" t="n">
+      <c r="AP5" t="n">
         <v>-0.0126910136354993</v>
       </c>
-      <c r="AP5" t="n">
+      <c r="AQ5" t="n">
         <v>-0.0894390540455207</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AR5" t="n">
         <v>-0.0101994742962003</v>
       </c>
-      <c r="AR5" t="n">
+      <c r="AS5" t="n">
         <v>-0.0112512269908156</v>
       </c>
-      <c r="AS5" t="n">
+      <c r="AT5" t="n">
         <v>0.0000448609568320835</v>
       </c>
-      <c r="AT5" t="n">
+      <c r="AU5" t="n">
         <v>-0.498559310609352</v>
       </c>
-      <c r="AU5" t="n">
+      <c r="AV5" t="n">
         <v>-0.805638210882072</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="AW5" t="n">
         <v>-0.120809715617533</v>
       </c>
-      <c r="AW5" t="n">
+      <c r="AX5" t="n">
         <v>-0.0301455181868558</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B6" t="n">
         <v>0.00645129629028539</v>
@@ -1327,99 +1345,102 @@
         <v>0.0251407537430236</v>
       </c>
       <c r="T6" t="n">
+        <v>-0.0699200947123337</v>
+      </c>
+      <c r="U6" t="n">
         <v>0.0139718914512606</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>-0.000132894999783394</v>
       </c>
-      <c r="V6" t="n">
+      <c r="W6" t="n">
         <v>0.00645129629028539</v>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>-0.0740218264774652</v>
       </c>
-      <c r="X6" t="n">
+      <c r="Y6" t="n">
         <v>-0.426109778443417</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>-0.00863925898046138</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AA6" t="n">
         <v>-2.62102808522828</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AB6" t="n">
         <v>-6.8923058608767</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AC6" t="n">
         <v>0.137803941295357</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AD6" t="n">
         <v>0.136375350030841</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AE6" t="n">
         <v>-0.0151404486111813</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AF6" t="n">
         <v>-0.122453111385131</v>
       </c>
-      <c r="AF6" t="n">
+      <c r="AG6" t="n">
         <v>-0.0227025532079354</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="AH6" t="n">
         <v>-0.596281488285481</v>
       </c>
-      <c r="AH6" t="n">
+      <c r="AI6" t="n">
         <v>0.00645129629028539</v>
       </c>
-      <c r="AI6" t="n">
+      <c r="AJ6" t="n">
         <v>0.645115029604612</v>
       </c>
-      <c r="AJ6" t="n">
+      <c r="AK6" t="n">
         <v>-3.15401967973663</v>
       </c>
-      <c r="AK6" t="n">
+      <c r="AL6" t="n">
         <v>-0.479314393113188</v>
       </c>
-      <c r="AL6" t="n">
+      <c r="AM6" t="n">
         <v>0.611713139250937</v>
       </c>
-      <c r="AM6" t="n">
+      <c r="AN6" t="n">
         <v>-16.3729940487149</v>
       </c>
-      <c r="AN6" t="n">
+      <c r="AO6" t="n">
         <v>0.00645129629028539</v>
       </c>
-      <c r="AO6" t="n">
+      <c r="AP6" t="n">
         <v>-0.0145101640738114</v>
       </c>
-      <c r="AP6" t="n">
+      <c r="AQ6" t="n">
         <v>-0.0878933964847373</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AR6" t="n">
         <v>0.00932060029867682</v>
       </c>
-      <c r="AR6" t="n">
+      <c r="AS6" t="n">
         <v>0.00381549939108643</v>
       </c>
-      <c r="AS6" t="n">
+      <c r="AT6" t="n">
         <v>0.00806407023915974</v>
       </c>
-      <c r="AT6" t="n">
+      <c r="AU6" t="n">
         <v>0.0874724920290433</v>
       </c>
-      <c r="AU6" t="n">
+      <c r="AV6" t="n">
         <v>-0.190520132930576</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="AW6" t="n">
         <v>0.0388849601319051</v>
       </c>
-      <c r="AW6" t="n">
+      <c r="AX6" t="n">
         <v>0.011774904127128</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B7" t="n">
         <v>0.00814176389116344</v>
@@ -1476,99 +1497,102 @@
         <v>0.110974802955842</v>
       </c>
       <c r="T7" t="n">
+        <v>0.0281535754509545</v>
+      </c>
+      <c r="U7" t="n">
         <v>-0.000876495039657422</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>-0.00620743716453717</v>
       </c>
-      <c r="V7" t="n">
+      <c r="W7" t="n">
         <v>0.00814176389116344</v>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>-0.283340517880106</v>
       </c>
-      <c r="X7" t="n">
+      <c r="Y7" t="n">
         <v>0.138975754240142</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>-0.00159461831557265</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AA7" t="n">
         <v>-4.9668067447289</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AB7" t="n">
         <v>-7.22304860551217</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AC7" t="n">
         <v>0.417680620231473</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AD7" t="n">
         <v>0.423753622457581</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AE7" t="n">
         <v>-0.00435850361499742</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AF7" t="n">
         <v>0.288568308229093</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AG7" t="n">
         <v>0.158753315312689</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AH7" t="n">
         <v>0.197079987747135</v>
       </c>
-      <c r="AH7" t="n">
+      <c r="AI7" t="n">
         <v>0.00814176389116344</v>
       </c>
-      <c r="AI7" t="n">
+      <c r="AJ7" t="n">
         <v>1.13742322544659</v>
       </c>
-      <c r="AJ7" t="n">
+      <c r="AK7" t="n">
         <v>-5.9815866905914</v>
       </c>
-      <c r="AK7" t="n">
+      <c r="AL7" t="n">
         <v>2.17142306102353</v>
       </c>
-      <c r="AL7" t="n">
+      <c r="AM7" t="n">
         <v>1.55919121343083</v>
       </c>
-      <c r="AM7" t="n">
+      <c r="AN7" t="n">
         <v>-32.8114717861355</v>
       </c>
-      <c r="AN7" t="n">
+      <c r="AO7" t="n">
         <v>0.00814176389116344</v>
       </c>
-      <c r="AO7" t="n">
+      <c r="AP7" t="n">
         <v>-0.0488867604947774</v>
       </c>
-      <c r="AP7" t="n">
+      <c r="AQ7" t="n">
         <v>-0.130889359225575</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AR7" t="n">
         <v>-0.0270952994673804</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="AS7" t="n">
         <v>0.036756012010565</v>
       </c>
-      <c r="AS7" t="n">
+      <c r="AT7" t="n">
         <v>0.0264964849976002</v>
       </c>
-      <c r="AT7" t="n">
+      <c r="AU7" t="n">
         <v>0.356836304294275</v>
       </c>
-      <c r="AU7" t="n">
+      <c r="AV7" t="n">
         <v>-0.56377954951785</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="AW7" t="n">
         <v>-0.106160778920502</v>
       </c>
-      <c r="AW7" t="n">
+      <c r="AX7" t="n">
         <v>-0.0501658689365992</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B8" t="n">
         <v>0.0510175523324224</v>
@@ -1625,99 +1649,102 @@
         <v>0.0905617445971902</v>
       </c>
       <c r="T8" t="n">
+        <v>0.00096796600931647</v>
+      </c>
+      <c r="U8" t="n">
         <v>-0.00209657549514964</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>-0.00677780817797705</v>
       </c>
-      <c r="V8" t="n">
+      <c r="W8" t="n">
         <v>0.0510175523324224</v>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>-0.0179969006256854</v>
       </c>
-      <c r="X8" t="n">
+      <c r="Y8" t="n">
         <v>1.72478003474691</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>0.0323052094194796</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AA8" t="n">
         <v>-8.95649637019016</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AB8" t="n">
         <v>-16.3473555096506</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AC8" t="n">
         <v>-1.96231738904952</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AD8" t="n">
         <v>-1.89565515953533</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AE8" t="n">
         <v>-0.0229033995739873</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AF8" t="n">
         <v>-1.89738612961306</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AG8" t="n">
         <v>-1.22631104841774</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AH8" t="n">
         <v>-0.81200803808392</v>
       </c>
-      <c r="AH8" t="n">
+      <c r="AI8" t="n">
         <v>0.0510175523324224</v>
       </c>
-      <c r="AI8" t="n">
+      <c r="AJ8" t="n">
         <v>11.114539057225</v>
       </c>
-      <c r="AJ8" t="n">
+      <c r="AK8" t="n">
         <v>-8.1921204196342</v>
       </c>
-      <c r="AK8" t="n">
+      <c r="AL8" t="n">
         <v>1.91725271712848</v>
       </c>
-      <c r="AL8" t="n">
+      <c r="AM8" t="n">
         <v>1.2301571278282</v>
       </c>
-      <c r="AM8" t="n">
+      <c r="AN8" t="n">
         <v>-14.5716415236272</v>
       </c>
-      <c r="AN8" t="n">
+      <c r="AO8" t="n">
         <v>0.0510175523324224</v>
       </c>
-      <c r="AO8" t="n">
+      <c r="AP8" t="n">
         <v>0.0070596788647981</v>
       </c>
-      <c r="AP8" t="n">
+      <c r="AQ8" t="n">
         <v>0.623298285383439</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AR8" t="n">
         <v>0.126299451263104</v>
       </c>
-      <c r="AR8" t="n">
+      <c r="AS8" t="n">
         <v>0.0144864590925036</v>
       </c>
-      <c r="AS8" t="n">
+      <c r="AT8" t="n">
         <v>-0.00241545656382177</v>
       </c>
-      <c r="AT8" t="n">
+      <c r="AU8" t="n">
         <v>-0.364200052676681</v>
       </c>
-      <c r="AU8" t="n">
+      <c r="AV8" t="n">
         <v>0.868272419517312</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="AW8" t="n">
         <v>0.332533194885255</v>
       </c>
-      <c r="AW8" t="n">
+      <c r="AX8" t="n">
         <v>0.103441942041893</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B9" t="n">
         <v>-0.0165178602451828</v>
@@ -1774,99 +1801,102 @@
         <v>0.0417863572476073</v>
       </c>
       <c r="T9" t="n">
+        <v>0.0249620883401492</v>
+      </c>
+      <c r="U9" t="n">
         <v>-0.000853934485337494</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>-0.00619126760761209</v>
       </c>
-      <c r="V9" t="n">
+      <c r="W9" t="n">
         <v>-0.0165178602451828</v>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>0.117661170908875</v>
       </c>
-      <c r="X9" t="n">
+      <c r="Y9" t="n">
         <v>-0.316776579339672</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>-0.0560367343376188</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AA9" t="n">
         <v>-0.642977014608471</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AB9" t="n">
         <v>24.8075123968551</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AC9" t="n">
         <v>1.05843136508607</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AD9" t="n">
         <v>1.06447099286481</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AE9" t="n">
         <v>-0.00394236784617542</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AF9" t="n">
         <v>0.786101660215013</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AG9" t="n">
         <v>0.697507361040615</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AH9" t="n">
         <v>-0.0378910393975687</v>
       </c>
-      <c r="AH9" t="n">
+      <c r="AI9" t="n">
         <v>-0.0165178602451828</v>
       </c>
-      <c r="AI9" t="n">
+      <c r="AJ9" t="n">
         <v>-1.66707982254063</v>
       </c>
-      <c r="AJ9" t="n">
+      <c r="AK9" t="n">
         <v>-0.0627951798163674</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="AL9" t="n">
         <v>-0.202045598243233</v>
       </c>
-      <c r="AL9" t="n">
+      <c r="AM9" t="n">
         <v>-0.343026876426291</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="AN9" t="n">
         <v>-38.8813346529616</v>
       </c>
-      <c r="AN9" t="n">
+      <c r="AO9" t="n">
         <v>-0.0165178602451828</v>
       </c>
-      <c r="AO9" t="n">
+      <c r="AP9" t="n">
         <v>-0.0311334277035191</v>
       </c>
-      <c r="AP9" t="n">
+      <c r="AQ9" t="n">
         <v>-0.085991106624436</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AR9" t="n">
         <v>-0.0372883416236204</v>
       </c>
-      <c r="AR9" t="n">
+      <c r="AS9" t="n">
         <v>-0.00671792788632267</v>
       </c>
-      <c r="AS9" t="n">
+      <c r="AT9" t="n">
         <v>0.00187555546266787</v>
       </c>
-      <c r="AT9" t="n">
+      <c r="AU9" t="n">
         <v>-0.0201674683720062</v>
       </c>
-      <c r="AU9" t="n">
+      <c r="AV9" t="n">
         <v>-0.560270477376811</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="AW9" t="n">
         <v>-0.065809910687646</v>
       </c>
-      <c r="AW9" t="n">
+      <c r="AX9" t="n">
         <v>-0.0495860187344967</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B10" t="n">
         <v>-0.0126666021447166</v>
@@ -1923,99 +1953,102 @@
         <v>0.0279753954941065</v>
       </c>
       <c r="T10" t="n">
+        <v>-0.0343197792230875</v>
+      </c>
+      <c r="U10" t="n">
         <v>-0.00494730670772397</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>-0.0059363948616229</v>
       </c>
-      <c r="V10" t="n">
+      <c r="W10" t="n">
         <v>-0.0126666021447166</v>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>-0.034254738347036</v>
       </c>
-      <c r="X10" t="n">
+      <c r="Y10" t="n">
         <v>-0.318820967683793</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>0.00288103584039171</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AA10" t="n">
         <v>9.18313302274477</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AB10" t="n">
         <v>2.60604523920295</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AC10" t="n">
         <v>0.0993920276010099</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AD10" t="n">
         <v>0.0649110900285878</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AE10" t="n">
         <v>-0.00601580844399689</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AF10" t="n">
         <v>0.121246255656583</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AG10" t="n">
         <v>0.0824696836727371</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AH10" t="n">
         <v>0.324413975954479</v>
       </c>
-      <c r="AH10" t="n">
+      <c r="AI10" t="n">
         <v>-0.0126666021447166</v>
       </c>
-      <c r="AI10" t="n">
+      <c r="AJ10" t="n">
         <v>-3.3738464829268</v>
       </c>
-      <c r="AJ10" t="n">
+      <c r="AK10" t="n">
         <v>0.109681635244063</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="AL10" t="n">
         <v>-1.06939568123992</v>
       </c>
-      <c r="AL10" t="n">
+      <c r="AM10" t="n">
         <v>-0.97502565826004</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="AN10" t="n">
         <v>20.6358648362426</v>
       </c>
-      <c r="AN10" t="n">
+      <c r="AO10" t="n">
         <v>-0.0126666021447166</v>
       </c>
-      <c r="AO10" t="n">
+      <c r="AP10" t="n">
         <v>0.0162128674262684</v>
       </c>
-      <c r="AP10" t="n">
+      <c r="AQ10" t="n">
         <v>-0.0685088524170304</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AR10" t="n">
         <v>-0.0184782945022104</v>
       </c>
-      <c r="AR10" t="n">
+      <c r="AS10" t="n">
         <v>-0.00562302260810126</v>
       </c>
-      <c r="AS10" t="n">
+      <c r="AT10" t="n">
         <v>-0.00229376249545885</v>
       </c>
-      <c r="AT10" t="n">
+      <c r="AU10" t="n">
         <v>0.226312930238288</v>
       </c>
-      <c r="AU10" t="n">
+      <c r="AV10" t="n">
         <v>0.25487024586806</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="AW10" t="n">
         <v>-0.106321546072497</v>
       </c>
-      <c r="AW10" t="n">
+      <c r="AX10" t="n">
         <v>0.000659318827429851</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B11" t="n">
         <v>-0.00347800705486099</v>
@@ -2072,99 +2105,102 @@
         <v>0.0237553759118981</v>
       </c>
       <c r="T11" t="n">
+        <v>-0.134530072267207</v>
+      </c>
+      <c r="U11" t="n">
         <v>0.0161860205464844</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>0.0534106065636256</v>
       </c>
-      <c r="V11" t="n">
+      <c r="W11" t="n">
         <v>-0.00347800705486099</v>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>-0.0356350520085281</v>
       </c>
-      <c r="X11" t="n">
+      <c r="Y11" t="n">
         <v>0.130356101422482</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>-0.0171102899495</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AA11" t="n">
         <v>6.46159713625299</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AB11" t="n">
         <v>-3.79001194417842</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AC11" t="n">
         <v>-0.280277339731389</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AD11" t="n">
         <v>-0.315375631341959</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AE11" t="n">
         <v>-0.01606426181088</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AF11" t="n">
         <v>-0.268974540442095</v>
       </c>
-      <c r="AF11" t="n">
+      <c r="AG11" t="n">
         <v>-0.198117667048756</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AH11" t="n">
         <v>-0.485241215412147</v>
       </c>
-      <c r="AH11" t="n">
+      <c r="AI11" t="n">
         <v>-0.00347800705486099</v>
       </c>
-      <c r="AI11" t="n">
+      <c r="AJ11" t="n">
         <v>-1.43196146583946</v>
       </c>
-      <c r="AJ11" t="n">
+      <c r="AK11" t="n">
         <v>5.93171983273495</v>
       </c>
-      <c r="AK11" t="n">
+      <c r="AL11" t="n">
         <v>-0.906522357558994</v>
       </c>
-      <c r="AL11" t="n">
+      <c r="AM11" t="n">
         <v>-0.824336869597266</v>
       </c>
-      <c r="AM11" t="n">
+      <c r="AN11" t="n">
         <v>65.2698455856311</v>
       </c>
-      <c r="AN11" t="n">
+      <c r="AO11" t="n">
         <v>-0.00347800705486099</v>
       </c>
-      <c r="AO11" t="n">
+      <c r="AP11" t="n">
         <v>0.00419728519968035</v>
       </c>
-      <c r="AP11" t="n">
+      <c r="AQ11" t="n">
         <v>-0.0794655684818871</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AR11" t="n">
         <v>0.00781679675748731</v>
       </c>
-      <c r="AR11" t="n">
+      <c r="AS11" t="n">
         <v>0.0287309003037915</v>
       </c>
-      <c r="AS11" t="n">
+      <c r="AT11" t="n">
         <v>0.00568403486323562</v>
       </c>
-      <c r="AT11" t="n">
+      <c r="AU11" t="n">
         <v>0.134164225856</v>
       </c>
-      <c r="AU11" t="n">
+      <c r="AV11" t="n">
         <v>0.48231177072471</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="AW11" t="n">
         <v>-0.00973001332228931</v>
       </c>
-      <c r="AW11" t="n">
+      <c r="AX11" t="n">
         <v>0.0317574067545379</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B12" t="n">
         <v>0.0290340072791658</v>
@@ -2221,99 +2257,102 @@
         <v>0.0845725423401366</v>
       </c>
       <c r="T12" t="n">
+        <v>-0.195773945622883</v>
+      </c>
+      <c r="U12" t="n">
         <v>-0.0158064113019022</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>-0.00992309874196714</v>
       </c>
-      <c r="V12" t="n">
+      <c r="W12" t="n">
         <v>0.0290340072791658</v>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>0.102569215250328</v>
       </c>
-      <c r="X12" t="n">
+      <c r="Y12" t="n">
         <v>1.02881316815924</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>0.0251369998132533</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AA12" t="n">
         <v>10.4443502682577</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AB12" t="n">
         <v>-11.8150048192469</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AC12" t="n">
         <v>-1.96199186569072</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AD12" t="n">
         <v>-1.8949825304987</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AE12" t="n">
         <v>-0.0242905439731241</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AF12" t="n">
         <v>-1.59590615976577</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AG12" t="n">
         <v>-1.22759840189505</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AH12" t="n">
         <v>-1.3537273060739</v>
       </c>
-      <c r="AH12" t="n">
+      <c r="AI12" t="n">
         <v>0.0290340072791658</v>
       </c>
-      <c r="AI12" t="n">
+      <c r="AJ12" t="n">
         <v>4.26920532369115</v>
       </c>
-      <c r="AJ12" t="n">
+      <c r="AK12" t="n">
         <v>6.78588885711216</v>
       </c>
-      <c r="AK12" t="n">
+      <c r="AL12" t="n">
         <v>3.26215139466083</v>
       </c>
-      <c r="AL12" t="n">
+      <c r="AM12" t="n">
         <v>1.15774783364925</v>
       </c>
-      <c r="AM12" t="n">
+      <c r="AN12" t="n">
         <v>70.4542453034088</v>
       </c>
-      <c r="AN12" t="n">
+      <c r="AO12" t="n">
         <v>0.0290340072791658</v>
       </c>
-      <c r="AO12" t="n">
+      <c r="AP12" t="n">
         <v>-0.0156950042196849</v>
       </c>
-      <c r="AP12" t="n">
+      <c r="AQ12" t="n">
         <v>0.0503504948466361</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AR12" t="n">
         <v>0.0319092339051696</v>
       </c>
-      <c r="AR12" t="n">
+      <c r="AS12" t="n">
         <v>0.0302245199374329</v>
       </c>
-      <c r="AS12" t="n">
+      <c r="AT12" t="n">
         <v>0.00599980181313706</v>
       </c>
-      <c r="AT12" t="n">
+      <c r="AU12" t="n">
         <v>0.283915495752221</v>
       </c>
-      <c r="AU12" t="n">
+      <c r="AV12" t="n">
         <v>1.25725739989224</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="AW12" t="n">
         <v>0.198453286570986</v>
       </c>
-      <c r="AW12" t="n">
+      <c r="AX12" t="n">
         <v>0.0695752226753227</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B13" t="n">
         <v>-0.022420261701553</v>
@@ -2370,93 +2409,96 @@
         <v>-0.168424724444471</v>
       </c>
       <c r="T13" t="n">
+        <v>0.188928968681322</v>
+      </c>
+      <c r="U13" t="n">
         <v>-0.00310887118567709</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>-0.0104389664730564</v>
       </c>
-      <c r="V13" t="n">
+      <c r="W13" t="n">
         <v>-0.022420261701553</v>
       </c>
-      <c r="W13" t="n">
+      <c r="X13" t="n">
         <v>0.0996129393258328</v>
       </c>
-      <c r="X13" t="n">
+      <c r="Y13" t="n">
         <v>-0.636789414539381</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="Z13" t="n">
         <v>-0.000535905416495116</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AA13" t="n">
         <v>-8.92496448610394</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AB13" t="n">
         <v>10.5679640030331</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AC13" t="n">
         <v>1.0654007533225</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AD13" t="n">
         <v>1.04508319890403</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AE13" t="n">
         <v>0.104684631324917</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AF13" t="n">
         <v>1.24391823479601</v>
       </c>
-      <c r="AF13" t="n">
+      <c r="AG13" t="n">
         <v>0.837362146580173</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="AH13" t="n">
         <v>1.87034141716541</v>
       </c>
-      <c r="AH13" t="n">
+      <c r="AI13" t="n">
         <v>-0.022420261701553</v>
       </c>
-      <c r="AI13" t="n">
+      <c r="AJ13" t="n">
         <v>-3.69809949426058</v>
       </c>
-      <c r="AJ13" t="n">
+      <c r="AK13" t="n">
         <v>2.40170986082051</v>
       </c>
-      <c r="AK13" t="n">
+      <c r="AL13" t="n">
         <v>-0.699027958914593</v>
       </c>
-      <c r="AL13" t="n">
+      <c r="AM13" t="n">
         <v>-0.594911104085817</v>
       </c>
-      <c r="AM13" t="n">
+      <c r="AN13" t="n">
         <v>-10.8398832885408</v>
       </c>
-      <c r="AN13" t="n">
+      <c r="AO13" t="n">
         <v>-0.022420261701553</v>
       </c>
-      <c r="AO13" t="n">
+      <c r="AP13" t="n">
         <v>0.0235227963443035</v>
       </c>
-      <c r="AP13" t="n">
+      <c r="AQ13" t="n">
         <v>-0.0129243837296623</v>
       </c>
-      <c r="AQ13" t="n">
+      <c r="AR13" t="n">
         <v>-0.0411016566401093</v>
       </c>
-      <c r="AR13" t="n">
+      <c r="AS13" t="n">
         <v>-0.0332452111152857</v>
       </c>
-      <c r="AS13" t="n">
+      <c r="AT13" t="n">
         <v>-0.0110944784640508</v>
       </c>
-      <c r="AT13" t="n">
+      <c r="AU13" t="n">
         <v>-0.149526899565437</v>
       </c>
-      <c r="AU13" t="n">
+      <c r="AV13" t="n">
         <v>-0.513702335853815</v>
       </c>
-      <c r="AV13" t="n">
+      <c r="AW13" t="n">
         <v>-0.111200809177955</v>
       </c>
-      <c r="AW13" t="n">
+      <c r="AX13" t="n">
         <v>-0.034822419453474</v>
       </c>
     </row>
